--- a/reports/Debug-purgatory-20260106/For The Week Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260106/For The Week Ending (Prior Year)_Revenue.xlsx
@@ -100,10 +100,10 @@
     <t>account</t>
   </si>
   <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T101</t>
-  </si>
-  <si>
-    <t>T100</t>
   </si>
   <si>
     <t>department</t>
@@ -584,7 +584,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="2">
-        <v>1434.18</v>
+        <v>97871.13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -598,7 +598,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="2">
-        <v>97871.13</v>
+        <v>1434.18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
